--- a/src/evaluation/data/processed/RES_policy_maker_model_travel_time_from_sample_to_hospital.xlsx
+++ b/src/evaluation/data/processed/RES_policy_maker_model_travel_time_from_sample_to_hospital.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>49.257259</v>
+        <v>49.25726</v>
       </c>
       <c r="F2" t="n">
         <v>6.852541</v>
@@ -518,10 +518,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>49.26812930661734</v>
+        <v>49.26813</v>
       </c>
       <c r="F3" t="n">
-        <v>6.929470619593767</v>
+        <v>6.929471</v>
       </c>
       <c r="G3" t="n">
         <v>7.28</v>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>49.237085</v>
+        <v>49.23709</v>
       </c>
       <c r="F4" t="n">
         <v>6.99259</v>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>49.153009</v>
+        <v>49.15301</v>
       </c>
       <c r="F5" t="n">
         <v>7.048336</v>
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>49.297734</v>
+        <v>49.29773</v>
       </c>
       <c r="F6" t="n">
         <v>7.054714</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49.495769</v>
+        <v>49.49577</v>
       </c>
       <c r="F7" t="n">
         <v>6.596771</v>
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>49.495769</v>
+        <v>49.49577</v>
       </c>
       <c r="F8" t="n">
         <v>6.596771</v>
@@ -698,13 +698,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>49.457186</v>
+        <v>49.45719</v>
       </c>
       <c r="F9" t="n">
         <v>6.631578</v>
       </c>
       <c r="G9" t="n">
-        <v>11.96</v>
+        <v>11.97</v>
       </c>
       <c r="H9" t="n">
         <v>11.2</v>
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>49.457186</v>
+        <v>49.45719</v>
       </c>
       <c r="F10" t="n">
         <v>6.631578</v>
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>49.537868</v>
+        <v>49.53787</v>
       </c>
       <c r="F11" t="n">
         <v>6.88934</v>
@@ -788,10 +788,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>49.33767769818895</v>
+        <v>49.33768</v>
       </c>
       <c r="F12" t="n">
-        <v>7.005279273288449</v>
+        <v>7.005279</v>
       </c>
       <c r="G12" t="n">
         <v>9.699999999999999</v>
@@ -818,10 +818,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>49.33767769818895</v>
+        <v>49.33768</v>
       </c>
       <c r="F13" t="n">
-        <v>7.005279273288449</v>
+        <v>7.005279</v>
       </c>
       <c r="G13" t="n">
         <v>11.74</v>
@@ -848,13 +848,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>49.40973615864516</v>
+        <v>49.40974</v>
       </c>
       <c r="F14" t="n">
-        <v>7.172516962777409</v>
+        <v>7.172517</v>
       </c>
       <c r="G14" t="n">
-        <v>13.47</v>
+        <v>13.02</v>
       </c>
       <c r="H14" t="n">
         <v>6.28</v>
@@ -878,10 +878,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>49.40973615864516</v>
+        <v>49.40974</v>
       </c>
       <c r="F15" t="n">
-        <v>7.172516962777409</v>
+        <v>7.172517</v>
       </c>
       <c r="G15" t="n">
         <v>6.42</v>
@@ -908,13 +908,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>49.39718981222195</v>
+        <v>49.39719</v>
       </c>
       <c r="F16" t="n">
-        <v>7.213364346793378</v>
+        <v>7.213364</v>
       </c>
       <c r="G16" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="H16" t="n">
         <v>2.79</v>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>49.266127</v>
+        <v>49.26613</v>
       </c>
       <c r="F17" t="n">
         <v>6.68297</v>
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>49.328624</v>
+        <v>49.32862</v>
       </c>
       <c r="F18" t="n">
         <v>6.714977</v>
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>49.315236</v>
+        <v>49.31524</v>
       </c>
       <c r="F19" t="n">
         <v>6.756487</v>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>49.35666769333056</v>
+        <v>49.35667</v>
       </c>
       <c r="F20" t="n">
-        <v>6.822620825380222</v>
+        <v>6.822621</v>
       </c>
       <c r="G20" t="n">
         <v>15.68</v>
@@ -1058,13 +1058,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>49.44208949482798</v>
+        <v>49.44209</v>
       </c>
       <c r="F21" t="n">
-        <v>6.904224529034402</v>
+        <v>6.904225</v>
       </c>
       <c r="G21" t="n">
-        <v>4.69</v>
+        <v>4.8</v>
       </c>
       <c r="H21" t="n">
         <v>2.45</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>49.153009</v>
+        <v>49.15301</v>
       </c>
       <c r="F22" t="n">
         <v>7.048336</v>
@@ -1118,16 +1118,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>49.290552</v>
+        <v>49.29055</v>
       </c>
       <c r="F23" t="n">
         <v>7.113175</v>
       </c>
       <c r="G23" t="n">
-        <v>26.42</v>
+        <v>26.35</v>
       </c>
       <c r="H23" t="n">
-        <v>13.56</v>
+        <v>13.54</v>
       </c>
     </row>
     <row r="24">
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>49.317756</v>
+        <v>49.31776</v>
       </c>
       <c r="F24" t="n">
         <v>7.227015</v>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>49.317756</v>
+        <v>49.31776</v>
       </c>
       <c r="F25" t="n">
         <v>7.227015</v>
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>49.3762045599062</v>
+        <v>49.3762</v>
       </c>
       <c r="F26" t="n">
-        <v>7.280034712412421</v>
+        <v>7.280035</v>
       </c>
       <c r="G26" t="n">
         <v>20.54</v>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>49.537868</v>
+        <v>49.53787</v>
       </c>
       <c r="F27" t="n">
         <v>6.88934</v>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>49.537868</v>
+        <v>49.53787</v>
       </c>
       <c r="F28" t="n">
         <v>6.88934</v>
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>49.453979</v>
+        <v>49.45398</v>
       </c>
       <c r="F29" t="n">
         <v>7.178492</v>
@@ -1328,7 +1328,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>49.454659</v>
+        <v>49.45466</v>
       </c>
       <c r="F30" t="n">
         <v>7.186793</v>
@@ -1358,7 +1358,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>49.454659</v>
+        <v>49.45466</v>
       </c>
       <c r="F31" t="n">
         <v>7.186793</v>
